--- a/transfer/excel_export/sweep_node2_20261014_180352.xlsx
+++ b/transfer/excel_export/sweep_node2_20261014_180352.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R193"/>
+  <dimension ref="A1:T193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,6 +507,16 @@
           <t>目標端原類別_Recall</t>
         </is>
       </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Clean_F1</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>Clean_Recall</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -565,6 +575,12 @@
       <c r="R2" t="n">
         <v>0.95</v>
       </c>
+      <c r="S2" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -623,6 +639,12 @@
       <c r="R3" t="n">
         <v>0.95</v>
       </c>
+      <c r="S3" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -681,6 +703,12 @@
       <c r="R4" t="n">
         <v>0.95</v>
       </c>
+      <c r="S4" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -739,6 +767,12 @@
       <c r="R5" t="n">
         <v>0.95</v>
       </c>
+      <c r="S5" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -797,6 +831,12 @@
       <c r="R6" t="n">
         <v>0.95</v>
       </c>
+      <c r="S6" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -855,6 +895,12 @@
       <c r="R7" t="n">
         <v>0.95</v>
       </c>
+      <c r="S7" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -913,6 +959,12 @@
       <c r="R8" t="n">
         <v>0.95</v>
       </c>
+      <c r="S8" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -971,6 +1023,12 @@
       <c r="R9" t="n">
         <v>0.95</v>
       </c>
+      <c r="S9" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1029,6 +1087,12 @@
       <c r="R10" t="n">
         <v>0.95</v>
       </c>
+      <c r="S10" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1087,6 +1151,12 @@
       <c r="R11" t="n">
         <v>0.95</v>
       </c>
+      <c r="S11" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1145,6 +1215,12 @@
       <c r="R12" t="n">
         <v>0.95</v>
       </c>
+      <c r="S12" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1203,6 +1279,12 @@
       <c r="R13" t="n">
         <v>0.95</v>
       </c>
+      <c r="S13" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1261,6 +1343,12 @@
       <c r="R14" t="n">
         <v>0.95</v>
       </c>
+      <c r="S14" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1319,6 +1407,12 @@
       <c r="R15" t="n">
         <v>0.95</v>
       </c>
+      <c r="S15" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1377,6 +1471,12 @@
       <c r="R16" t="n">
         <v>0.95</v>
       </c>
+      <c r="S16" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1435,6 +1535,12 @@
       <c r="R17" t="n">
         <v>0.95</v>
       </c>
+      <c r="S17" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1493,6 +1599,12 @@
       <c r="R18" t="n">
         <v>0.95</v>
       </c>
+      <c r="S18" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1551,6 +1663,12 @@
       <c r="R19" t="n">
         <v>0.95</v>
       </c>
+      <c r="S19" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1609,6 +1727,12 @@
       <c r="R20" t="n">
         <v>0.95</v>
       </c>
+      <c r="S20" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1667,6 +1791,12 @@
       <c r="R21" t="n">
         <v>0.95</v>
       </c>
+      <c r="S21" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1725,6 +1855,12 @@
       <c r="R22" t="n">
         <v>0.95</v>
       </c>
+      <c r="S22" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1783,6 +1919,12 @@
       <c r="R23" t="n">
         <v>0.95</v>
       </c>
+      <c r="S23" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1841,6 +1983,12 @@
       <c r="R24" t="n">
         <v>0.95</v>
       </c>
+      <c r="S24" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1899,6 +2047,12 @@
       <c r="R25" t="n">
         <v>0.95</v>
       </c>
+      <c r="S25" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1957,6 +2111,12 @@
       <c r="R26" t="n">
         <v>0.95</v>
       </c>
+      <c r="S26" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2015,6 +2175,12 @@
       <c r="R27" t="n">
         <v>0.95</v>
       </c>
+      <c r="S27" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2073,6 +2239,12 @@
       <c r="R28" t="n">
         <v>0.95</v>
       </c>
+      <c r="S28" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2131,6 +2303,12 @@
       <c r="R29" t="n">
         <v>0.95</v>
       </c>
+      <c r="S29" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2189,6 +2367,12 @@
       <c r="R30" t="n">
         <v>0.95</v>
       </c>
+      <c r="S30" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2247,6 +2431,12 @@
       <c r="R31" t="n">
         <v>0.95</v>
       </c>
+      <c r="S31" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2305,6 +2495,12 @@
       <c r="R32" t="n">
         <v>0.95</v>
       </c>
+      <c r="S32" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2363,6 +2559,12 @@
       <c r="R33" t="n">
         <v>0.95</v>
       </c>
+      <c r="S33" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2421,6 +2623,12 @@
       <c r="R34" t="n">
         <v>0.95</v>
       </c>
+      <c r="S34" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2479,6 +2687,12 @@
       <c r="R35" t="n">
         <v>0.95</v>
       </c>
+      <c r="S35" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2537,6 +2751,12 @@
       <c r="R36" t="n">
         <v>0.95</v>
       </c>
+      <c r="S36" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2595,6 +2815,12 @@
       <c r="R37" t="n">
         <v>0.95</v>
       </c>
+      <c r="S37" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2653,6 +2879,12 @@
       <c r="R38" t="n">
         <v>0.95</v>
       </c>
+      <c r="S38" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2711,6 +2943,12 @@
       <c r="R39" t="n">
         <v>0.95</v>
       </c>
+      <c r="S39" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2769,6 +3007,12 @@
       <c r="R40" t="n">
         <v>0.95</v>
       </c>
+      <c r="S40" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T40" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2827,6 +3071,12 @@
       <c r="R41" t="n">
         <v>0.95</v>
       </c>
+      <c r="S41" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T41" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2885,6 +3135,12 @@
       <c r="R42" t="n">
         <v>0.95</v>
       </c>
+      <c r="S42" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T42" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2943,6 +3199,12 @@
       <c r="R43" t="n">
         <v>0.95</v>
       </c>
+      <c r="S43" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T43" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3001,6 +3263,12 @@
       <c r="R44" t="n">
         <v>0.95</v>
       </c>
+      <c r="S44" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T44" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3059,6 +3327,12 @@
       <c r="R45" t="n">
         <v>0.95</v>
       </c>
+      <c r="S45" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T45" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3117,6 +3391,12 @@
       <c r="R46" t="n">
         <v>0.95</v>
       </c>
+      <c r="S46" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T46" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3175,6 +3455,12 @@
       <c r="R47" t="n">
         <v>0.95</v>
       </c>
+      <c r="S47" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T47" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3233,6 +3519,12 @@
       <c r="R48" t="n">
         <v>0.95</v>
       </c>
+      <c r="S48" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T48" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3291,6 +3583,12 @@
       <c r="R49" t="n">
         <v>0.95</v>
       </c>
+      <c r="S49" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T49" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3349,6 +3647,12 @@
       <c r="R50" t="n">
         <v>0.95</v>
       </c>
+      <c r="S50" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T50" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3407,6 +3711,12 @@
       <c r="R51" t="n">
         <v>0.95</v>
       </c>
+      <c r="S51" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T51" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3465,6 +3775,12 @@
       <c r="R52" t="n">
         <v>0.95</v>
       </c>
+      <c r="S52" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T52" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3523,6 +3839,12 @@
       <c r="R53" t="n">
         <v>0.95</v>
       </c>
+      <c r="S53" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T53" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3581,6 +3903,12 @@
       <c r="R54" t="n">
         <v>0.95</v>
       </c>
+      <c r="S54" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T54" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3639,6 +3967,12 @@
       <c r="R55" t="n">
         <v>0.95</v>
       </c>
+      <c r="S55" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T55" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3697,6 +4031,12 @@
       <c r="R56" t="n">
         <v>0.95</v>
       </c>
+      <c r="S56" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T56" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3755,6 +4095,12 @@
       <c r="R57" t="n">
         <v>0.95</v>
       </c>
+      <c r="S57" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T57" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3813,6 +4159,12 @@
       <c r="R58" t="n">
         <v>0.95</v>
       </c>
+      <c r="S58" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T58" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3871,6 +4223,12 @@
       <c r="R59" t="n">
         <v>0.95</v>
       </c>
+      <c r="S59" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T59" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3929,6 +4287,12 @@
       <c r="R60" t="n">
         <v>0.95</v>
       </c>
+      <c r="S60" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T60" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3987,6 +4351,12 @@
       <c r="R61" t="n">
         <v>0.95</v>
       </c>
+      <c r="S61" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T61" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4045,6 +4415,12 @@
       <c r="R62" t="n">
         <v>0.95</v>
       </c>
+      <c r="S62" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T62" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -4103,6 +4479,12 @@
       <c r="R63" t="n">
         <v>0.95</v>
       </c>
+      <c r="S63" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T63" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4161,6 +4543,12 @@
       <c r="R64" t="n">
         <v>0.95</v>
       </c>
+      <c r="S64" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T64" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4219,6 +4607,12 @@
       <c r="R65" t="n">
         <v>0.95</v>
       </c>
+      <c r="S65" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T65" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4277,6 +4671,12 @@
       <c r="R66" t="n">
         <v>0.95</v>
       </c>
+      <c r="S66" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T66" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -4335,6 +4735,12 @@
       <c r="R67" t="n">
         <v>0.95</v>
       </c>
+      <c r="S67" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T67" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4393,6 +4799,12 @@
       <c r="R68" t="n">
         <v>0.95</v>
       </c>
+      <c r="S68" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T68" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4451,6 +4863,12 @@
       <c r="R69" t="n">
         <v>0.95</v>
       </c>
+      <c r="S69" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T69" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4509,6 +4927,12 @@
       <c r="R70" t="n">
         <v>0.95</v>
       </c>
+      <c r="S70" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T70" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4567,6 +4991,12 @@
       <c r="R71" t="n">
         <v>0.95</v>
       </c>
+      <c r="S71" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T71" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4625,6 +5055,12 @@
       <c r="R72" t="n">
         <v>0.95</v>
       </c>
+      <c r="S72" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T72" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4683,6 +5119,12 @@
       <c r="R73" t="n">
         <v>0.95</v>
       </c>
+      <c r="S73" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T73" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4741,6 +5183,12 @@
       <c r="R74" t="n">
         <v>0.95</v>
       </c>
+      <c r="S74" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T74" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4799,6 +5247,12 @@
       <c r="R75" t="n">
         <v>0.95</v>
       </c>
+      <c r="S75" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4857,6 +5311,12 @@
       <c r="R76" t="n">
         <v>0.95</v>
       </c>
+      <c r="S76" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T76" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4915,6 +5375,12 @@
       <c r="R77" t="n">
         <v>0.95</v>
       </c>
+      <c r="S77" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T77" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4973,6 +5439,12 @@
       <c r="R78" t="n">
         <v>0.95</v>
       </c>
+      <c r="S78" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T78" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -5031,6 +5503,12 @@
       <c r="R79" t="n">
         <v>0.95</v>
       </c>
+      <c r="S79" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T79" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -5089,6 +5567,12 @@
       <c r="R80" t="n">
         <v>0.95</v>
       </c>
+      <c r="S80" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T80" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -5147,6 +5631,12 @@
       <c r="R81" t="n">
         <v>0.95</v>
       </c>
+      <c r="S81" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T81" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -5205,6 +5695,12 @@
       <c r="R82" t="n">
         <v>0.95</v>
       </c>
+      <c r="S82" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T82" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -5263,6 +5759,12 @@
       <c r="R83" t="n">
         <v>0.95</v>
       </c>
+      <c r="S83" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T83" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -5321,6 +5823,12 @@
       <c r="R84" t="n">
         <v>0.95</v>
       </c>
+      <c r="S84" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T84" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -5379,6 +5887,12 @@
       <c r="R85" t="n">
         <v>0.95</v>
       </c>
+      <c r="S85" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T85" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -5437,6 +5951,12 @@
       <c r="R86" t="n">
         <v>0.95</v>
       </c>
+      <c r="S86" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T86" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -5495,6 +6015,12 @@
       <c r="R87" t="n">
         <v>0.95</v>
       </c>
+      <c r="S87" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T87" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -5553,6 +6079,12 @@
       <c r="R88" t="n">
         <v>0.95</v>
       </c>
+      <c r="S88" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T88" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -5611,6 +6143,12 @@
       <c r="R89" t="n">
         <v>0.95</v>
       </c>
+      <c r="S89" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T89" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -5669,6 +6207,12 @@
       <c r="R90" t="n">
         <v>0.95</v>
       </c>
+      <c r="S90" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T90" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -5727,6 +6271,12 @@
       <c r="R91" t="n">
         <v>0.95</v>
       </c>
+      <c r="S91" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T91" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -5785,6 +6335,12 @@
       <c r="R92" t="n">
         <v>0.95</v>
       </c>
+      <c r="S92" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T92" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -5843,6 +6399,12 @@
       <c r="R93" t="n">
         <v>0.95</v>
       </c>
+      <c r="S93" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T93" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -5901,6 +6463,12 @@
       <c r="R94" t="n">
         <v>0.95</v>
       </c>
+      <c r="S94" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T94" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5959,6 +6527,12 @@
       <c r="R95" t="n">
         <v>0.95</v>
       </c>
+      <c r="S95" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T95" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -6017,6 +6591,12 @@
       <c r="R96" t="n">
         <v>0.95</v>
       </c>
+      <c r="S96" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T96" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -6075,6 +6655,12 @@
       <c r="R97" t="n">
         <v>0.95</v>
       </c>
+      <c r="S97" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T97" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -6133,6 +6719,12 @@
       <c r="R98" t="n">
         <v>0.95</v>
       </c>
+      <c r="S98" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T98" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -6191,6 +6783,12 @@
       <c r="R99" t="n">
         <v>0.95</v>
       </c>
+      <c r="S99" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T99" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -6249,6 +6847,12 @@
       <c r="R100" t="n">
         <v>0.95</v>
       </c>
+      <c r="S100" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T100" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -6307,6 +6911,12 @@
       <c r="R101" t="n">
         <v>0.95</v>
       </c>
+      <c r="S101" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T101" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -6365,6 +6975,12 @@
       <c r="R102" t="n">
         <v>0.95</v>
       </c>
+      <c r="S102" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T102" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -6423,6 +7039,12 @@
       <c r="R103" t="n">
         <v>0.95</v>
       </c>
+      <c r="S103" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T103" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -6481,6 +7103,12 @@
       <c r="R104" t="n">
         <v>0.95</v>
       </c>
+      <c r="S104" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T104" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -6539,6 +7167,12 @@
       <c r="R105" t="n">
         <v>0.95</v>
       </c>
+      <c r="S105" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T105" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -6597,6 +7231,12 @@
       <c r="R106" t="n">
         <v>0.95</v>
       </c>
+      <c r="S106" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T106" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -6655,6 +7295,12 @@
       <c r="R107" t="n">
         <v>0.95</v>
       </c>
+      <c r="S107" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T107" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -6713,6 +7359,12 @@
       <c r="R108" t="n">
         <v>0.95</v>
       </c>
+      <c r="S108" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T108" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -6771,6 +7423,12 @@
       <c r="R109" t="n">
         <v>0.95</v>
       </c>
+      <c r="S109" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T109" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -6829,6 +7487,12 @@
       <c r="R110" t="n">
         <v>0.95</v>
       </c>
+      <c r="S110" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T110" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -6887,6 +7551,12 @@
       <c r="R111" t="n">
         <v>0.95</v>
       </c>
+      <c r="S111" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T111" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -6945,6 +7615,12 @@
       <c r="R112" t="n">
         <v>0.95</v>
       </c>
+      <c r="S112" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T112" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -7003,6 +7679,12 @@
       <c r="R113" t="n">
         <v>0.95</v>
       </c>
+      <c r="S113" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T113" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -7061,6 +7743,12 @@
       <c r="R114" t="n">
         <v>0.95</v>
       </c>
+      <c r="S114" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T114" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -7119,6 +7807,12 @@
       <c r="R115" t="n">
         <v>0.95</v>
       </c>
+      <c r="S115" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T115" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -7177,6 +7871,12 @@
       <c r="R116" t="n">
         <v>0.95</v>
       </c>
+      <c r="S116" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T116" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -7235,6 +7935,12 @@
       <c r="R117" t="n">
         <v>0.95</v>
       </c>
+      <c r="S117" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -7293,6 +7999,12 @@
       <c r="R118" t="n">
         <v>0.95</v>
       </c>
+      <c r="S118" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -7351,6 +8063,12 @@
       <c r="R119" t="n">
         <v>0.95</v>
       </c>
+      <c r="S119" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -7409,6 +8127,12 @@
       <c r="R120" t="n">
         <v>0.95</v>
       </c>
+      <c r="S120" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -7467,6 +8191,12 @@
       <c r="R121" t="n">
         <v>0.95</v>
       </c>
+      <c r="S121" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -7525,6 +8255,12 @@
       <c r="R122" t="n">
         <v>0.95</v>
       </c>
+      <c r="S122" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -7583,6 +8319,12 @@
       <c r="R123" t="n">
         <v>0.95</v>
       </c>
+      <c r="S123" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -7641,6 +8383,12 @@
       <c r="R124" t="n">
         <v>0.95</v>
       </c>
+      <c r="S124" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -7699,6 +8447,12 @@
       <c r="R125" t="n">
         <v>0.95</v>
       </c>
+      <c r="S125" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -7757,6 +8511,12 @@
       <c r="R126" t="n">
         <v>0.95</v>
       </c>
+      <c r="S126" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -7815,6 +8575,12 @@
       <c r="R127" t="n">
         <v>0.95</v>
       </c>
+      <c r="S127" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -7873,6 +8639,12 @@
       <c r="R128" t="n">
         <v>0.95</v>
       </c>
+      <c r="S128" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -7931,6 +8703,12 @@
       <c r="R129" t="n">
         <v>0.95</v>
       </c>
+      <c r="S129" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -7989,6 +8767,12 @@
       <c r="R130" t="n">
         <v>0.95</v>
       </c>
+      <c r="S130" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -8047,6 +8831,12 @@
       <c r="R131" t="n">
         <v>0.95</v>
       </c>
+      <c r="S131" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -8105,6 +8895,12 @@
       <c r="R132" t="n">
         <v>0.95</v>
       </c>
+      <c r="S132" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -8163,6 +8959,12 @@
       <c r="R133" t="n">
         <v>0.95</v>
       </c>
+      <c r="S133" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -8221,6 +9023,12 @@
       <c r="R134" t="n">
         <v>0.95</v>
       </c>
+      <c r="S134" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -8279,6 +9087,12 @@
       <c r="R135" t="n">
         <v>0.95</v>
       </c>
+      <c r="S135" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -8337,6 +9151,12 @@
       <c r="R136" t="n">
         <v>0.95</v>
       </c>
+      <c r="S136" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -8395,6 +9215,12 @@
       <c r="R137" t="n">
         <v>0.95</v>
       </c>
+      <c r="S137" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -8453,6 +9279,12 @@
       <c r="R138" t="n">
         <v>0.95</v>
       </c>
+      <c r="S138" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -8511,6 +9343,12 @@
       <c r="R139" t="n">
         <v>0.95</v>
       </c>
+      <c r="S139" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -8569,6 +9407,12 @@
       <c r="R140" t="n">
         <v>0.95</v>
       </c>
+      <c r="S140" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -8627,6 +9471,12 @@
       <c r="R141" t="n">
         <v>0.95</v>
       </c>
+      <c r="S141" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -8685,6 +9535,12 @@
       <c r="R142" t="n">
         <v>0.95</v>
       </c>
+      <c r="S142" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -8743,6 +9599,12 @@
       <c r="R143" t="n">
         <v>0.95</v>
       </c>
+      <c r="S143" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -8801,6 +9663,12 @@
       <c r="R144" t="n">
         <v>0.95</v>
       </c>
+      <c r="S144" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T144" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -8859,6 +9727,12 @@
       <c r="R145" t="n">
         <v>0.95</v>
       </c>
+      <c r="S145" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T145" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -8917,6 +9791,12 @@
       <c r="R146" t="n">
         <v>0.95</v>
       </c>
+      <c r="S146" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T146" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -8975,6 +9855,12 @@
       <c r="R147" t="n">
         <v>0.95</v>
       </c>
+      <c r="S147" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T147" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -9033,6 +9919,12 @@
       <c r="R148" t="n">
         <v>0.95</v>
       </c>
+      <c r="S148" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T148" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -9091,6 +9983,12 @@
       <c r="R149" t="n">
         <v>0.95</v>
       </c>
+      <c r="S149" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T149" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -9149,6 +10047,12 @@
       <c r="R150" t="n">
         <v>0.95</v>
       </c>
+      <c r="S150" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T150" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -9207,6 +10111,12 @@
       <c r="R151" t="n">
         <v>0.95</v>
       </c>
+      <c r="S151" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T151" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -9265,6 +10175,12 @@
       <c r="R152" t="n">
         <v>0.95</v>
       </c>
+      <c r="S152" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T152" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -9323,6 +10239,12 @@
       <c r="R153" t="n">
         <v>0.95</v>
       </c>
+      <c r="S153" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T153" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -9381,6 +10303,12 @@
       <c r="R154" t="n">
         <v>0.95</v>
       </c>
+      <c r="S154" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T154" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -9439,6 +10367,12 @@
       <c r="R155" t="n">
         <v>0.95</v>
       </c>
+      <c r="S155" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T155" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -9497,6 +10431,12 @@
       <c r="R156" t="n">
         <v>0.95</v>
       </c>
+      <c r="S156" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T156" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -9555,6 +10495,12 @@
       <c r="R157" t="n">
         <v>0.95</v>
       </c>
+      <c r="S157" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T157" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -9613,6 +10559,12 @@
       <c r="R158" t="n">
         <v>0.95</v>
       </c>
+      <c r="S158" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T158" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -9671,6 +10623,12 @@
       <c r="R159" t="n">
         <v>0.95</v>
       </c>
+      <c r="S159" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T159" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -9729,6 +10687,12 @@
       <c r="R160" t="n">
         <v>0.95</v>
       </c>
+      <c r="S160" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T160" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -9787,6 +10751,12 @@
       <c r="R161" t="n">
         <v>0.95</v>
       </c>
+      <c r="S161" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T161" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -9845,6 +10815,12 @@
       <c r="R162" t="n">
         <v>0.95</v>
       </c>
+      <c r="S162" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T162" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -9903,6 +10879,12 @@
       <c r="R163" t="n">
         <v>0.95</v>
       </c>
+      <c r="S163" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T163" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -9961,6 +10943,12 @@
       <c r="R164" t="n">
         <v>0.95</v>
       </c>
+      <c r="S164" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T164" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -10019,6 +11007,12 @@
       <c r="R165" t="n">
         <v>0.95</v>
       </c>
+      <c r="S165" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T165" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -10077,6 +11071,12 @@
       <c r="R166" t="n">
         <v>0.95</v>
       </c>
+      <c r="S166" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T166" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -10135,6 +11135,12 @@
       <c r="R167" t="n">
         <v>0.95</v>
       </c>
+      <c r="S167" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T167" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -10193,6 +11199,12 @@
       <c r="R168" t="n">
         <v>0.95</v>
       </c>
+      <c r="S168" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T168" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -10251,6 +11263,12 @@
       <c r="R169" t="n">
         <v>0.95</v>
       </c>
+      <c r="S169" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T169" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -10309,6 +11327,12 @@
       <c r="R170" t="n">
         <v>0.95</v>
       </c>
+      <c r="S170" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T170" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -10367,6 +11391,12 @@
       <c r="R171" t="n">
         <v>0.95</v>
       </c>
+      <c r="S171" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T171" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -10425,6 +11455,12 @@
       <c r="R172" t="n">
         <v>0.95</v>
       </c>
+      <c r="S172" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T172" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -10483,6 +11519,12 @@
       <c r="R173" t="n">
         <v>0.95</v>
       </c>
+      <c r="S173" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T173" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -10541,6 +11583,12 @@
       <c r="R174" t="n">
         <v>0.95</v>
       </c>
+      <c r="S174" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T174" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -10599,6 +11647,12 @@
       <c r="R175" t="n">
         <v>0.95</v>
       </c>
+      <c r="S175" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T175" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -10657,6 +11711,12 @@
       <c r="R176" t="n">
         <v>0.95</v>
       </c>
+      <c r="S176" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T176" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -10715,6 +11775,12 @@
       <c r="R177" t="n">
         <v>0.95</v>
       </c>
+      <c r="S177" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T177" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -10773,6 +11839,12 @@
       <c r="R178" t="n">
         <v>0.95</v>
       </c>
+      <c r="S178" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T178" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -10831,6 +11903,12 @@
       <c r="R179" t="n">
         <v>0.95</v>
       </c>
+      <c r="S179" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T179" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -10889,6 +11967,12 @@
       <c r="R180" t="n">
         <v>0.95</v>
       </c>
+      <c r="S180" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T180" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -10947,6 +12031,12 @@
       <c r="R181" t="n">
         <v>0.95</v>
       </c>
+      <c r="S181" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T181" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -11005,6 +12095,12 @@
       <c r="R182" t="n">
         <v>0.95</v>
       </c>
+      <c r="S182" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T182" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -11063,6 +12159,12 @@
       <c r="R183" t="n">
         <v>0.95</v>
       </c>
+      <c r="S183" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T183" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -11121,6 +12223,12 @@
       <c r="R184" t="n">
         <v>0.95</v>
       </c>
+      <c r="S184" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T184" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -11179,6 +12287,12 @@
       <c r="R185" t="n">
         <v>0.95</v>
       </c>
+      <c r="S185" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T185" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -11237,6 +12351,12 @@
       <c r="R186" t="n">
         <v>0.95</v>
       </c>
+      <c r="S186" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T186" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -11295,6 +12415,12 @@
       <c r="R187" t="n">
         <v>0.95</v>
       </c>
+      <c r="S187" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T187" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -11353,6 +12479,12 @@
       <c r="R188" t="n">
         <v>0.95</v>
       </c>
+      <c r="S188" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T188" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -11411,6 +12543,12 @@
       <c r="R189" t="n">
         <v>0.95</v>
       </c>
+      <c r="S189" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T189" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -11469,6 +12607,12 @@
       <c r="R190" t="n">
         <v>0.95</v>
       </c>
+      <c r="S190" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T190" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -11527,6 +12671,12 @@
       <c r="R191" t="n">
         <v>0.95</v>
       </c>
+      <c r="S191" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T191" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -11585,6 +12735,12 @@
       <c r="R192" t="n">
         <v>0.95</v>
       </c>
+      <c r="S192" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T192" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -11619,7 +12775,6 @@
       <c r="H193" t="n">
         <v>10</v>
       </c>
-      <c r="I193" t="inlineStr"/>
       <c r="J193" t="n">
         <v>0.8392857142857143</v>
       </c>
@@ -11638,12 +12793,17 @@
       <c r="O193" t="n">
         <v>0</v>
       </c>
-      <c r="P193" t="inlineStr"/>
       <c r="Q193" t="n">
         <v>0.926829268292683</v>
       </c>
       <c r="R193" t="n">
         <v>0.95</v>
+      </c>
+      <c r="S193" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="T193" t="n">
+        <v>0.9</v>
       </c>
     </row>
   </sheetData>
